--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/phi-4/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/phi-4/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D2">
-        <v>306</v>
+        <v>345</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="D3">
-        <v>230</v>
+        <v>254</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="H3">
         <v>426</v>
